--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DDV_HRM-2031-0100/Panel 7/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DDV_HRM-2031-0100/Panel 7/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
@@ -455,13 +455,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.6791</v>
+        <v>16.71077</v>
       </c>
       <c r="D2" t="n">
         <v>16.20082</v>
       </c>
       <c r="E2" t="n">
-        <v>16.71077</v>
+        <v>16.6791</v>
       </c>
       <c r="F2" t="n">
         <v>22.07825</v>
@@ -690,13 +690,13 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>16.88799</v>
+      </c>
+      <c r="D12" t="n">
         <v>16.34951</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>16.57711</v>
-      </c>
-      <c r="E12" t="n">
-        <v>16.88799</v>
       </c>
       <c r="F12" t="n">
         <v>41.89787</v>
@@ -768,10 +768,10 @@
         <v>16.81136</v>
       </c>
       <c r="D15" t="n">
+        <v>16.51197</v>
+      </c>
+      <c r="E15" t="n">
         <v>16.5449</v>
-      </c>
-      <c r="E15" t="n">
-        <v>16.51197</v>
       </c>
       <c r="F15" t="n">
         <v>41.67098</v>
@@ -818,10 +818,10 @@
         <v>17.18853</v>
       </c>
       <c r="D17" t="n">
+        <v>16.47227</v>
+      </c>
+      <c r="E17" t="n">
         <v>16.91469</v>
-      </c>
-      <c r="E17" t="n">
-        <v>16.47227</v>
       </c>
       <c r="F17" t="n">
         <v>42.87918</v>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>16.86459</v>
+      </c>
+      <c r="D18" t="n">
         <v>16.71558</v>
-      </c>
-      <c r="D18" t="n">
-        <v>16.86459</v>
       </c>
       <c r="E18" t="n">
         <v>16.84583</v>
@@ -868,10 +868,10 @@
         <v>16.70793</v>
       </c>
       <c r="D19" t="n">
+        <v>16.51818</v>
+      </c>
+      <c r="E19" t="n">
         <v>16.60459</v>
-      </c>
-      <c r="E19" t="n">
-        <v>16.51818</v>
       </c>
       <c r="F19" t="n">
         <v>42.45891</v>
@@ -890,13 +890,13 @@
         </is>
       </c>
       <c r="C20" t="n">
+        <v>16.6686</v>
+      </c>
+      <c r="D20" t="n">
         <v>16.44518</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>16.4654</v>
-      </c>
-      <c r="E20" t="n">
-        <v>16.6686</v>
       </c>
       <c r="F20" t="n">
         <v>42.24317</v>
